--- a/assets/docs/lop5/Tieng Viet - Lop 5.xlsx
+++ b/assets/docs/lop5/Tieng Viet - Lop 5.xlsx
@@ -2702,12 +2702,7 @@
           <t>60+61</t>
         </is>
       </c>
-      <c r="H55" s="4" t="inlineStr">
-        <is>
-          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Khi ôn về từ đa nghĩa, GV mở từ điển tiếng Việt bản điện tử và gõ một từ nhiều nghĩa như từ chân, từ mắt
-Năng lực số Miền 5 (Cơ bản, bậc 2): GV mở bài tập tương tác nối câu với nghĩa đúng của từ nhiều nghĩa trong câu đó; máy chấm ngay nên HS nhận ra mình còn nhầm nghĩa chuyển với từ đồng âm</t>
-        </is>
-      </c>
+      <c r="H55" s="4" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="4" t="inlineStr">
@@ -2816,7 +2811,8 @@
       <c r="H58" s="4" t="inlineStr">
         <is>
           <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Trước bài đọc “Thư gửi các học sinh”, GV chiếu tranh chủ điểm và ảnh tư liệu ngày khai giảng đầu tiên của nước ta sau năm 1945 do thầy cô chọn từ nguồn…
-Năng lực số Miền 2 (Cơ bản, bậc 2): GV ghi âm lượt đọc diễn cảm của vài HS rồi mở lại cho cả lớp nghe; các em nhận xét theo tiêu chí chiếu sẵn là đọc trang trọng</t>
+Năng lực số Miền 2 (Cơ bản, bậc 2): GV ghi âm lượt đọc diễn cảm của vài HS rồi mở lại cho cả lớp nghe; các em nhận xét theo tiêu chí chiếu sẵn là đọc trang trọng
+Học tập và làm theo Bác: Điều 2 “Học tập tốt, lao động tốt” (mạch 1, 2): từ câu trả lời “Vì sao Bác khuyên HS cố gắng siêng năng học tập?”, HS nói việc học của mình góp phần gì cho đất nước và nêu một việc cụ thể sẽ làm để học tốt hơn trong tuần.</t>
         </is>
       </c>
     </row>
@@ -4332,7 +4328,7 @@
       </c>
       <c r="E94" s="4" t="inlineStr">
         <is>
-          <t>Chú ốc sên bay</t>
+          <t>Phim hoạt hình Chú ốc sên bay</t>
         </is>
       </c>
       <c r="F94" s="4" t="inlineStr">
